--- a/data/source/weekly/cs-en-us-115pct.xlsx
+++ b/data/source/weekly/cs-en-us-115pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,10 +905,10 @@
         <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-40</v>
+        <v>-25</v>
       </c>
       <c r="I15" s="14">
         <v>3</v>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-14.285714285714</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G16" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H16" s="15">
-        <v>23.529411764705</v>
+        <v>5.263157894736</v>
       </c>
       <c r="I16" s="14">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J16" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K16" s="15">
-        <v>31.818181818181</v>
+        <v>34.615384615384</v>
       </c>
       <c r="L16" s="15">
-        <v>-29.268292682926</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M16" s="15">
-        <v>-9.375</v>
+        <v>-14.634146341463</v>
       </c>
       <c r="N16" s="15">
-        <v>-79.861111111111</v>
+        <v>-80.113636363636</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
         <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G17" s="14">
         <v>29</v>
       </c>
       <c r="H17" s="15">
-        <v>-31.034482758620</v>
+        <v>-17.241379310344</v>
       </c>
       <c r="I17" s="14">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="J17" s="14">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="K17" s="15">
-        <v>-39.622641509434</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L17" s="15">
-        <v>-31.914893617021</v>
+        <v>-32.203389830508</v>
       </c>
       <c r="M17" s="15">
-        <v>23.076923076923</v>
+        <v>21.212121212121</v>
       </c>
       <c r="N17" s="15">
-        <v>-17.948717948717</v>
+        <v>-9.090909090909</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-57.142857142857</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
         <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>-76.470588235294</v>
+        <v>-70.588235294117</v>
       </c>
       <c r="I18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J18" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K18" s="15">
-        <v>-72.222222222222</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="L18" s="15">
-        <v>-80.769230769230</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="M18" s="15">
-        <v>-84.375</v>
+        <v>-82.857142857142</v>
       </c>
       <c r="N18" s="15">
-        <v>-98.366013071895</v>
+        <v>-98.295454545454</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>11</v>
+      </c>
+      <c r="D19" s="14">
         <v>14</v>
       </c>
-      <c r="D19" s="14">
-        <v>20</v>
-      </c>
       <c r="E19" s="15">
-        <v>-30</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="F19" s="14">
         <v>43</v>
       </c>
       <c r="G19" s="14">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H19" s="15">
-        <v>-27.118644067796</v>
+        <v>-28.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="J19" s="14">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="K19" s="15">
-        <v>-18.987341772151</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="L19" s="15">
-        <v>-49.206349206349</v>
+        <v>-45.255474452554</v>
       </c>
       <c r="M19" s="15">
-        <v>20.754716981132</v>
+        <v>25</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.8</v>
+        <v>-52.830188679245</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>250</v>
       </c>
       <c r="F20" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G20" s="14">
         <v>14</v>
       </c>
       <c r="H20" s="15">
-        <v>-28.571428571428</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I20" s="14">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J20" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K20" s="15">
-        <v>-16.666666666666</v>
+        <v>10</v>
       </c>
       <c r="L20" s="15">
-        <v>-51.612903225806</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>-40</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.589743589743</v>
+        <v>-91.881918819188</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>32</v>
       </c>
       <c r="D21" s="17">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E21" s="18">
-        <v>-30.434782608695</v>
+        <v>3.225806451612</v>
       </c>
       <c r="F21" s="17">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="G21" s="17">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H21" s="18">
-        <v>-29.370629370629</v>
+        <v>-25.517241379310</v>
       </c>
       <c r="I21" s="17">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="J21" s="17">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="K21" s="18">
-        <v>-25.252525252525</v>
+        <v>-20.960698689956</v>
       </c>
       <c r="L21" s="18">
-        <v>-45.985401459854</v>
+        <v>-40.655737704918</v>
       </c>
       <c r="M21" s="18">
-        <v>-13.450292397660</v>
+        <v>-9.045226130653</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.669789227166</v>
+        <v>-82.096933728981</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F22" s="14">
+        <v>5</v>
+      </c>
+      <c r="G22" s="14">
         <v>4</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>300</v>
-      </c>
-      <c r="F22" s="14">
-        <v>6</v>
-      </c>
-      <c r="G22" s="14">
-        <v>3</v>
-      </c>
       <c r="H22" s="15">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="L22" s="15">
-        <v>-33.333333333333</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M22" s="15">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1271,28 +1271,28 @@
         <v>-25</v>
       </c>
       <c r="F24" s="14">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G24" s="14">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H24" s="15">
-        <v>-34.482758620689</v>
+        <v>-38.842975206611</v>
       </c>
       <c r="I24" s="14">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="J24" s="14">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="K24" s="15">
-        <v>-23.809523809523</v>
+        <v>-24</v>
       </c>
       <c r="L24" s="15">
-        <v>-56.923076923076</v>
+        <v>-57.911392405063</v>
       </c>
       <c r="M24" s="15">
-        <v>0.900900900900</v>
+        <v>10.833333333333</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E25" s="15">
-        <v>-85.714285714285</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G25" s="14">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H25" s="15">
-        <v>-69.354838709677</v>
+        <v>-73.015873015873</v>
       </c>
       <c r="I25" s="14">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J25" s="14">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="K25" s="15">
-        <v>-69.444444444444</v>
+        <v>-65.476190476190</v>
       </c>
       <c r="L25" s="15">
-        <v>-86.335403726708</v>
+        <v>-85.051546391752</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D26" s="14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E26" s="15">
-        <v>13.636363636363</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="F26" s="14">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G26" s="14">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H26" s="15">
-        <v>-24.390243902439</v>
+        <v>-17.567567567567</v>
       </c>
       <c r="I26" s="14">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="J26" s="14">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="K26" s="15">
-        <v>-14.545454545454</v>
+        <v>-13.953488372093</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.476190476190</v>
+        <v>-13.953488372093</v>
       </c>
       <c r="M26" s="15">
-        <v>0</v>
+        <v>-0.892857142857</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="14">
         <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-25</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>4</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>300</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I28" s="14">
+        <v>10</v>
+      </c>
+      <c r="J28" s="14">
         <v>9</v>
       </c>
-      <c r="J28" s="14">
-        <v>7</v>
-      </c>
       <c r="K28" s="15">
-        <v>28.571428571428</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L28" s="15">
-        <v>-40</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-115pct.xlsx
+++ b/data/source/weekly/cs-en-us-115pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -864,7 +864,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-25</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>-50</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N15" s="15">
-        <v>-50</v>
+        <v>-16.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>2</v>
+      </c>
+      <c r="D16" s="14">
         <v>6</v>
       </c>
-      <c r="D16" s="14">
-        <v>4</v>
-      </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G16" s="14">
         <v>19</v>
       </c>
       <c r="H16" s="15">
-        <v>5.263157894736</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="I16" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J16" s="14">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K16" s="15">
-        <v>34.615384615384</v>
+        <v>12.5</v>
       </c>
       <c r="L16" s="15">
-        <v>-22.222222222222</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M16" s="15">
-        <v>-14.634146341463</v>
+        <v>-26.530612244898</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.113636363636</v>
+        <v>-81.909547738693</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G17" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H17" s="15">
-        <v>-17.241379310344</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="I17" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J17" s="14">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="K17" s="15">
-        <v>-33.333333333333</v>
+        <v>-37.681159420289</v>
       </c>
       <c r="L17" s="15">
-        <v>-32.203389830508</v>
+        <v>-32.8125</v>
       </c>
       <c r="M17" s="15">
-        <v>21.212121212121</v>
+        <v>22.857142857142</v>
       </c>
       <c r="N17" s="15">
-        <v>-9.090909090909</v>
+        <v>-20.370370370370</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-75</v>
+        <v>-40</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>-70.588235294117</v>
+        <v>-61.904761904761</v>
       </c>
       <c r="I18" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J18" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K18" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="L18" s="15">
         <v>-72.727272727272</v>
       </c>
-      <c r="L18" s="15">
-        <v>-78.571428571428</v>
-      </c>
       <c r="M18" s="15">
-        <v>-82.857142857142</v>
+        <v>-79.069767441860</v>
       </c>
       <c r="N18" s="15">
-        <v>-98.295454545454</v>
+        <v>-97.674418604651</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>-21.428571428571</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="F19" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G19" s="14">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H19" s="15">
-        <v>-28.333333333333</v>
+        <v>-26.984126984127</v>
       </c>
       <c r="I19" s="14">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="J19" s="14">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="K19" s="15">
-        <v>-19.354838709677</v>
+        <v>-17.924528301886</v>
       </c>
       <c r="L19" s="15">
-        <v>-45.255474452554</v>
+        <v>-44.230769230769</v>
       </c>
       <c r="M19" s="15">
-        <v>25</v>
+        <v>31.818181818181</v>
       </c>
       <c r="N19" s="15">
-        <v>-52.830188679245</v>
+        <v>-50.285714285714</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="F20" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G20" s="14">
         <v>14</v>
       </c>
       <c r="H20" s="15">
-        <v>-7.142857142857</v>
+        <v>21.428571428571</v>
       </c>
       <c r="I20" s="14">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J20" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K20" s="15">
-        <v>10</v>
+        <v>29.166666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-33.333333333333</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="M20" s="15">
-        <v>-18.518518518518</v>
+        <v>-6.060606060606</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.881918819188</v>
+        <v>-90.095846645367</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21" s="17">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E21" s="18">
-        <v>3.225806451612</v>
+        <v>-16.216216216216</v>
       </c>
       <c r="F21" s="17">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G21" s="17">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="H21" s="18">
-        <v>-25.517241379310</v>
+        <v>-25.165562913907</v>
       </c>
       <c r="I21" s="17">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="J21" s="17">
-        <v>229</v>
+        <v>266</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.960698689956</v>
+        <v>-20.676691729323</v>
       </c>
       <c r="L21" s="18">
-        <v>-40.655737704918</v>
+        <v>-38.304093567251</v>
       </c>
       <c r="M21" s="18">
-        <v>-9.045226130653</v>
+        <v>-7.860262008733</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.096933728981</v>
+        <v>-81.442392260334</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
       <c r="E22" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>5</v>
@@ -1201,10 +1201,10 @@
         <v>7</v>
       </c>
       <c r="J22" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K22" s="15">
-        <v>-12.5</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L22" s="15">
         <v>-22.222222222222</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E24" s="15">
-        <v>-25</v>
+        <v>16</v>
       </c>
       <c r="F24" s="14">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G24" s="14">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="H24" s="15">
-        <v>-38.842975206611</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="I24" s="14">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="J24" s="14">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="K24" s="15">
-        <v>-24</v>
+        <v>-19</v>
       </c>
       <c r="L24" s="15">
-        <v>-57.911392405063</v>
+        <v>-56.8</v>
       </c>
       <c r="M24" s="15">
-        <v>10.833333333333</v>
+        <v>19.117647058823</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>-41.666666666666</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F25" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G25" s="14">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="H25" s="15">
-        <v>-73.015873015873</v>
+        <v>-65.454545454545</v>
       </c>
       <c r="I25" s="14">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="J25" s="14">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="K25" s="15">
-        <v>-65.476190476190</v>
+        <v>-61.290322580645</v>
       </c>
       <c r="L25" s="15">
-        <v>-85.051546391752</v>
+        <v>-84.210526315789</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D26" s="14">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>-5.263157894736</v>
+        <v>70</v>
       </c>
       <c r="F26" s="14">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G26" s="14">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H26" s="15">
-        <v>-17.567567567567</v>
+        <v>-4.285714285714</v>
       </c>
       <c r="I26" s="14">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="J26" s="14">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K26" s="15">
-        <v>-13.953488372093</v>
+        <v>-7.913669064748</v>
       </c>
       <c r="L26" s="15">
-        <v>-13.953488372093</v>
+        <v>-12.328767123287</v>
       </c>
       <c r="M26" s="15">
-        <v>-0.892857142857</v>
+        <v>0.787401574803</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>2</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>100</v>
       </c>
       <c r="F27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>75</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I27" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="15">
+        <v>12.5</v>
+      </c>
+      <c r="L27" s="15">
         <v>0</v>
-      </c>
-      <c r="L27" s="15">
-        <v>-22.222222222222</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,7 +1429,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
         <v>-100</v>
@@ -1438,22 +1438,22 @@
         <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>20</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I28" s="14">
         <v>10</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>11.111111111111</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>-44.444444444444</v>
+        <v>-52.380952380952</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-115pct.xlsx
+++ b/data/source/weekly/cs-en-us-115pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
-      </c>
-      <c r="G15" s="14">
-        <v>2</v>
-      </c>
-      <c r="H15" s="15">
-        <v>100</v>
+        <v>5</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J15" s="14">
         <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>-16.666666666666</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>66.666666666666</v>
+        <v>75</v>
       </c>
       <c r="M15" s="15">
-        <v>66.666666666666</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-16.666666666666</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>-60</v>
       </c>
       <c r="F16" s="14">
         <v>15</v>
       </c>
       <c r="G16" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H16" s="15">
-        <v>-21.052631578947</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="I16" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J16" s="14">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K16" s="15">
-        <v>12.5</v>
+        <v>2.702702702702</v>
       </c>
       <c r="L16" s="15">
-        <v>-30.769230769230</v>
+        <v>-37.704918032786</v>
       </c>
       <c r="M16" s="15">
-        <v>-26.530612244898</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.909547738693</v>
+        <v>-82.407407407407</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E17" s="15">
-        <v>-66.666666666666</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F17" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G17" s="14">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H17" s="15">
-        <v>-25.806451612903</v>
+        <v>-27.027027027027</v>
       </c>
       <c r="I17" s="14">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="J17" s="14">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="K17" s="15">
-        <v>-37.681159420289</v>
+        <v>-36.585365853658</v>
       </c>
       <c r="L17" s="15">
-        <v>-32.8125</v>
+        <v>-34.177215189873</v>
       </c>
       <c r="M17" s="15">
-        <v>22.857142857142</v>
+        <v>23.809523809523</v>
       </c>
       <c r="N17" s="15">
-        <v>-20.370370370370</v>
+        <v>-10.344827586206</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,13 +1016,13 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
         <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-40</v>
+        <v>-80</v>
       </c>
       <c r="F18" s="14">
         <v>8</v>
@@ -1034,22 +1034,22 @@
         <v>-61.904761904761</v>
       </c>
       <c r="I18" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J18" s="14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K18" s="15">
-        <v>-66.666666666666</v>
+        <v>-65.625</v>
       </c>
       <c r="L18" s="15">
-        <v>-72.727272727272</v>
+        <v>-71.052631578947</v>
       </c>
       <c r="M18" s="15">
-        <v>-79.069767441860</v>
+        <v>-76.595744680851</v>
       </c>
       <c r="N18" s="15">
-        <v>-97.674418604651</v>
+        <v>-97.459584295612</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>-7.692307692307</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G19" s="14">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H19" s="15">
-        <v>-26.984126984127</v>
+        <v>-18.461538461538</v>
       </c>
       <c r="I19" s="14">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="J19" s="14">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="K19" s="15">
-        <v>-17.924528301886</v>
+        <v>-16.935483870967</v>
       </c>
       <c r="L19" s="15">
-        <v>-44.230769230769</v>
+        <v>-36.809815950920</v>
       </c>
       <c r="M19" s="15">
-        <v>31.818181818181</v>
+        <v>45.070422535211</v>
       </c>
       <c r="N19" s="15">
-        <v>-50.285714285714</v>
+        <v>-50.480769230769</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
         <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G20" s="14">
         <v>14</v>
       </c>
       <c r="H20" s="15">
-        <v>21.428571428571</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I20" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J20" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K20" s="15">
-        <v>29.166666666666</v>
+        <v>25</v>
       </c>
       <c r="L20" s="15">
-        <v>-8.823529411764</v>
+        <v>-5.405405405405</v>
       </c>
       <c r="M20" s="15">
-        <v>-6.060606060606</v>
+        <v>-5.405405405405</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.095846645367</v>
+        <v>-90.331491712707</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D21" s="17">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E21" s="18">
-        <v>-16.216216216216</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="G21" s="17">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H21" s="18">
-        <v>-25.165562913907</v>
+        <v>-19.496855345911</v>
       </c>
       <c r="I21" s="17">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="J21" s="17">
-        <v>266</v>
+        <v>311</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.676691729323</v>
+        <v>-20.900321543408</v>
       </c>
       <c r="L21" s="18">
-        <v>-38.304093567251</v>
+        <v>-35.602094240837</v>
       </c>
       <c r="M21" s="18">
-        <v>-7.860262008733</v>
+        <v>-2.380952380952</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.442392260334</v>
+        <v>-80.900621118012</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>5</v>
@@ -1207,7 +1207,7 @@
         <v>-22.222222222222</v>
       </c>
       <c r="L22" s="15">
-        <v>-22.222222222222</v>
+        <v>-30</v>
       </c>
       <c r="M22" s="15">
         <v>40</v>
@@ -1265,34 +1265,34 @@
         <v>29</v>
       </c>
       <c r="D24" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E24" s="15">
-        <v>16</v>
+        <v>7.407407407407</v>
       </c>
       <c r="F24" s="14">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="G24" s="14">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="H24" s="15">
-        <v>-26.315789473684</v>
+        <v>-9.259259259259</v>
       </c>
       <c r="I24" s="14">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="J24" s="14">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="K24" s="15">
-        <v>-19</v>
+        <v>-17.180616740088</v>
       </c>
       <c r="L24" s="15">
-        <v>-56.8</v>
+        <v>-55.868544600939</v>
       </c>
       <c r="M24" s="15">
-        <v>19.117647058823</v>
+        <v>18.987341772151</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E25" s="15">
-        <v>-22.222222222222</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G25" s="14">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="H25" s="15">
-        <v>-65.454545454545</v>
+        <v>-55.319148936170</v>
       </c>
       <c r="I25" s="14">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J25" s="14">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="K25" s="15">
-        <v>-61.290322580645</v>
+        <v>-60.952380952380</v>
       </c>
       <c r="L25" s="15">
-        <v>-84.210526315789</v>
+        <v>-84.230769230769</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E26" s="15">
-        <v>70</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="F26" s="14">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G26" s="14">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H26" s="15">
-        <v>-4.285714285714</v>
+        <v>9.230769230769</v>
       </c>
       <c r="I26" s="14">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="J26" s="14">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="K26" s="15">
-        <v>-7.913669064748</v>
+        <v>-9.150326797385</v>
       </c>
       <c r="L26" s="15">
-        <v>-12.328767123287</v>
+        <v>-19.186046511627</v>
       </c>
       <c r="M26" s="15">
-        <v>0.787401574803</v>
+        <v>-5.442176870748</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,29 +1387,29 @@
       <c r="C27" s="14">
         <v>2</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>7</v>
+      </c>
+      <c r="G27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="15">
-        <v>100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>8</v>
-      </c>
-      <c r="G27" s="14">
-        <v>3</v>
-      </c>
       <c r="H27" s="15">
-        <v>166.666666666667</v>
+        <v>600</v>
       </c>
       <c r="I27" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
         <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="L27" s="15">
         <v>0</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>4</v>
       </c>
       <c r="D28" s="14">
         <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H28" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J28" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>-52.380952380952</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1610,29 +1610,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>-100</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>21</v>
+      <c r="J33" s="14">
+        <v>1</v>
+      </c>
+      <c r="K33" s="15">
+        <v>0</v>
       </c>
       <c r="L33" s="15">
         <v>-50</v>

--- a/data/source/weekly/cs-en-us-115pct.xlsx
+++ b/data/source/weekly/cs-en-us-115pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,7 +902,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G16" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H16" s="15">
+        <v>-23.809523809523</v>
+      </c>
+      <c r="I16" s="14">
+        <v>45</v>
+      </c>
+      <c r="J16" s="14">
+        <v>43</v>
+      </c>
+      <c r="K16" s="15">
+        <v>4.651162790697</v>
+      </c>
+      <c r="L16" s="15">
         <v>-31.818181818181</v>
       </c>
-      <c r="I16" s="14">
-        <v>38</v>
-      </c>
-      <c r="J16" s="14">
-        <v>37</v>
-      </c>
-      <c r="K16" s="15">
-        <v>2.702702702702</v>
-      </c>
-      <c r="L16" s="15">
-        <v>-37.704918032786</v>
-      </c>
       <c r="M16" s="15">
-        <v>-26.923076923076</v>
+        <v>-19.642857142857</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.407407407407</v>
+        <v>-81.092436974789</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-30.769230769230</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G17" s="14">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H17" s="15">
-        <v>-27.027027027027</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I17" s="14">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="J17" s="14">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="K17" s="15">
-        <v>-36.585365853658</v>
+        <v>-32.954545454545</v>
       </c>
       <c r="L17" s="15">
-        <v>-34.177215189873</v>
+        <v>-32.183908045977</v>
       </c>
       <c r="M17" s="15">
-        <v>23.809523809523</v>
+        <v>22.916666666666</v>
       </c>
       <c r="N17" s="15">
-        <v>-10.344827586206</v>
+        <v>-6.349206349206</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H18" s="15">
-        <v>-61.904761904761</v>
+        <v>-43.75</v>
       </c>
       <c r="I18" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J18" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K18" s="15">
-        <v>-65.625</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="L18" s="15">
-        <v>-71.052631578947</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="M18" s="15">
-        <v>-76.595744680851</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="N18" s="15">
-        <v>-97.459584295612</v>
+        <v>-96.624472573839</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15">
-        <v>-16.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="14">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G19" s="14">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H19" s="15">
-        <v>-18.461538461538</v>
+        <v>-22.950819672131</v>
       </c>
       <c r="I19" s="14">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="J19" s="14">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="K19" s="15">
-        <v>-16.935483870967</v>
+        <v>-20.714285714285</v>
       </c>
       <c r="L19" s="15">
-        <v>-36.809815950920</v>
+        <v>-38.674033149171</v>
       </c>
       <c r="M19" s="15">
-        <v>45.070422535211</v>
+        <v>32.142857142857</v>
       </c>
       <c r="N19" s="15">
-        <v>-50.480769230769</v>
+        <v>-51.948051948051</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F20" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G20" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H20" s="15">
-        <v>42.857142857142</v>
+        <v>100</v>
       </c>
       <c r="I20" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J20" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K20" s="15">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="L20" s="15">
-        <v>-5.405405405405</v>
+        <v>-11.363636363636</v>
       </c>
       <c r="M20" s="15">
-        <v>-5.405405405405</v>
+        <v>-4.878048780487</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.331491712707</v>
+        <v>-90.346534653465</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D21" s="17">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E21" s="18">
-        <v>-26.666666666666</v>
+        <v>-15.625</v>
       </c>
       <c r="F21" s="17">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G21" s="17">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="H21" s="18">
-        <v>-19.496855345911</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="I21" s="17">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="J21" s="17">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.900321543408</v>
+        <v>-19.241982507288</v>
       </c>
       <c r="L21" s="18">
-        <v>-35.602094240837</v>
+        <v>-34.976525821596</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.380952380952</v>
+        <v>-2.464788732394</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.900621118012</v>
+        <v>-80.520393811533</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G22" s="14">
         <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>25</v>
+        <v>-75</v>
       </c>
       <c r="I22" s="14">
         <v>7</v>
       </c>
       <c r="J22" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K22" s="15">
-        <v>-22.222222222222</v>
+        <v>-30</v>
       </c>
       <c r="L22" s="15">
-        <v>-30</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>40</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>7.407407407407</v>
+        <v>19.047619047619</v>
       </c>
       <c r="F24" s="14">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G24" s="14">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="H24" s="15">
-        <v>-9.259259259259</v>
+        <v>-1.980198019801</v>
       </c>
       <c r="I24" s="14">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="J24" s="14">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="K24" s="15">
-        <v>-17.180616740088</v>
+        <v>-15.725806451612</v>
       </c>
       <c r="L24" s="15">
-        <v>-55.868544600939</v>
+        <v>-55.437100213219</v>
       </c>
       <c r="M24" s="15">
-        <v>18.987341772151</v>
+        <v>18.079096045197</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E25" s="15">
-        <v>-58.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="F25" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G25" s="14">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H25" s="15">
-        <v>-55.319148936170</v>
+        <v>-46.511627906976</v>
       </c>
       <c r="I25" s="14">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J25" s="14">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="K25" s="15">
-        <v>-60.952380952380</v>
+        <v>-60.869565217391</v>
       </c>
       <c r="L25" s="15">
-        <v>-84.230769230769</v>
+        <v>-84.320557491289</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E26" s="15">
-        <v>-21.428571428571</v>
+        <v>-76.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="G26" s="14">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="H26" s="15">
-        <v>9.230769230769</v>
+        <v>-27.397260273972</v>
       </c>
       <c r="I26" s="14">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J26" s="14">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="K26" s="15">
-        <v>-9.150326797385</v>
+        <v>-20.765027322404</v>
       </c>
       <c r="L26" s="15">
-        <v>-19.186046511627</v>
+        <v>-26.395939086294</v>
       </c>
       <c r="M26" s="15">
-        <v>-5.442176870748</v>
+        <v>-13.690476190476</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,13 +1394,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="I27" s="14">
         <v>10</v>
@@ -1412,7 +1412,7 @@
         <v>25</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>33.333333333333</v>
+        <v>200</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
         <v>9</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I28" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J28" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="L28" s="15">
-        <v>-31.818181818181</v>
+        <v>-28</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-115pct.xlsx
+++ b/data/source/weekly/cs-en-us-115pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,7 +902,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -911,22 +911,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
         <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>16.666666666666</v>
+        <v>50</v>
       </c>
       <c r="L15" s="15">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="M15" s="15">
-        <v>133.333333333333</v>
+        <v>200</v>
       </c>
       <c r="N15" s="15">
-        <v>-12.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
         <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G16" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H16" s="15">
-        <v>-23.809523809523</v>
+        <v>-47.826086956521</v>
       </c>
       <c r="I16" s="14">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J16" s="14">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K16" s="15">
-        <v>4.651162790697</v>
+        <v>-4.081632653061</v>
       </c>
       <c r="L16" s="15">
-        <v>-31.818181818181</v>
+        <v>-32.857142857142</v>
       </c>
       <c r="M16" s="15">
-        <v>-19.642857142857</v>
+        <v>-26.5625</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.092436974789</v>
+        <v>-81.782945736434</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G17" s="14">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="H17" s="15">
-        <v>-28.571428571428</v>
+        <v>-46.511627906976</v>
       </c>
       <c r="I17" s="14">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="J17" s="14">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="K17" s="15">
-        <v>-32.954545454545</v>
+        <v>-37.864077669902</v>
       </c>
       <c r="L17" s="15">
-        <v>-32.183908045977</v>
+        <v>-36.633663366336</v>
       </c>
       <c r="M17" s="15">
-        <v>22.916666666666</v>
+        <v>20.754716981132</v>
       </c>
       <c r="N17" s="15">
-        <v>-6.349206349206</v>
+        <v>-4.477611940298</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
-      </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
-      <c r="E18" s="15">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>-43.75</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J18" s="14">
         <v>34</v>
       </c>
       <c r="K18" s="15">
-        <v>-52.941176470588</v>
+        <v>-38.235294117647</v>
       </c>
       <c r="L18" s="15">
-        <v>-63.636363636363</v>
+        <v>-52.272727272727</v>
       </c>
       <c r="M18" s="15">
-        <v>-69.230769230769</v>
+        <v>-64.406779661017</v>
       </c>
       <c r="N18" s="15">
-        <v>-96.624472573839</v>
+        <v>-95.992366412213</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
         <v>-50</v>
       </c>
       <c r="F19" s="14">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G19" s="14">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H19" s="15">
-        <v>-22.950819672131</v>
+        <v>-29.824561403508</v>
       </c>
       <c r="I19" s="14">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="J19" s="14">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="K19" s="15">
-        <v>-20.714285714285</v>
+        <v>-22.666666666666</v>
       </c>
       <c r="L19" s="15">
-        <v>-38.674033149171</v>
+        <v>-41.414141414141</v>
       </c>
       <c r="M19" s="15">
-        <v>32.142857142857</v>
+        <v>28.888888888888</v>
       </c>
       <c r="N19" s="15">
-        <v>-51.948051948051</v>
+        <v>-52.263374485596</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G20" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>43.75</v>
       </c>
       <c r="I20" s="14">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J20" s="14">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K20" s="15">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L20" s="15">
-        <v>-11.363636363636</v>
+        <v>-4.255319148936</v>
       </c>
       <c r="M20" s="15">
-        <v>-4.878048780487</v>
+        <v>-2.173913043478</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.346534653465</v>
+        <v>-89.749430523918</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E21" s="18">
-        <v>-15.625</v>
+        <v>-35.135135135135</v>
       </c>
       <c r="F21" s="17">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="G21" s="17">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.793103448275</v>
+        <v>-22.516556291390</v>
       </c>
       <c r="I21" s="17">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="J21" s="17">
-        <v>343</v>
+        <v>380</v>
       </c>
       <c r="K21" s="18">
-        <v>-19.241982507288</v>
+        <v>-20.526315789473</v>
       </c>
       <c r="L21" s="18">
-        <v>-34.976525821596</v>
+        <v>-35.193133047210</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.464788732394</v>
+        <v>-4.126984126984</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.520393811533</v>
+        <v>-80.440414507772</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,34 +1183,34 @@
         <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" s="15">
         <v>-100</v>
       </c>
-      <c r="F22" s="14">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>7</v>
       </c>
       <c r="J22" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K22" s="15">
-        <v>-30</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="L22" s="15">
-        <v>-41.666666666666</v>
+        <v>-56.25</v>
       </c>
       <c r="M22" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>26</v>
+      </c>
+      <c r="D24" s="14">
         <v>25</v>
       </c>
-      <c r="D24" s="14">
-        <v>21</v>
-      </c>
       <c r="E24" s="15">
-        <v>19.047619047619</v>
+        <v>4</v>
       </c>
       <c r="F24" s="14">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G24" s="14">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H24" s="15">
-        <v>-1.980198019801</v>
+        <v>7.142857142857</v>
       </c>
       <c r="I24" s="14">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="J24" s="14">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="K24" s="15">
-        <v>-15.725806451612</v>
+        <v>-13.919413919413</v>
       </c>
       <c r="L24" s="15">
-        <v>-55.437100213219</v>
+        <v>-54.011741682974</v>
       </c>
       <c r="M24" s="15">
-        <v>18.079096045197</v>
+        <v>19.897959183673</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
         <v>10</v>
       </c>
       <c r="E25" s="15">
-        <v>-40</v>
+        <v>10</v>
       </c>
       <c r="F25" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G25" s="14">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H25" s="15">
-        <v>-46.511627906976</v>
+        <v>-34.146341463414</v>
       </c>
       <c r="I25" s="14">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="J25" s="14">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="K25" s="15">
-        <v>-60.869565217391</v>
+        <v>-55.2</v>
       </c>
       <c r="L25" s="15">
-        <v>-84.320557491289</v>
+        <v>-81.639344262295</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D26" s="14">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E26" s="15">
-        <v>-76.666666666666</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F26" s="14">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G26" s="14">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H26" s="15">
-        <v>-27.397260273972</v>
+        <v>-27.160493827160</v>
       </c>
       <c r="I26" s="14">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="J26" s="14">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="K26" s="15">
-        <v>-20.765027322404</v>
+        <v>-19.523809523809</v>
       </c>
       <c r="L26" s="15">
-        <v>-26.395939086294</v>
+        <v>-23.873873873873</v>
       </c>
       <c r="M26" s="15">
-        <v>-13.690476190476</v>
+        <v>-8.648648648648</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>2</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I27" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J27" s="14">
         <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L27" s="15">
-        <v>-9.090909090909</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
         <v>3</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
       <c r="E28" s="15">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>-11.111111111111</v>
+        <v>-20</v>
       </c>
       <c r="I28" s="14">
         <v>18</v>
       </c>
       <c r="J28" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>12.5</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="L28" s="15">
-        <v>-28</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="L33" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-115pct.xlsx
+++ b/data/source/weekly/cs-en-us-115pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -892,35 +892,35 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>3</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>6</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="G15" s="14">
+        <v>3</v>
+      </c>
+      <c r="H15" s="15">
+        <v>33.333333333333</v>
       </c>
       <c r="I15" s="14">
         <v>9</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M15" s="15">
         <v>200</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-83.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H16" s="15">
-        <v>-47.826086956521</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J16" s="14">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K16" s="15">
-        <v>-4.081632653061</v>
+        <v>-3.773584905660</v>
       </c>
       <c r="L16" s="15">
-        <v>-32.857142857142</v>
+        <v>-35.443037974683</v>
       </c>
       <c r="M16" s="15">
-        <v>-26.5625</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.782945736434</v>
+        <v>-82.291666666666</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>-66.666666666666</v>
+        <v>30</v>
       </c>
       <c r="F17" s="14">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G17" s="14">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H17" s="15">
-        <v>-46.511627906976</v>
+        <v>-25</v>
       </c>
       <c r="I17" s="14">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="J17" s="14">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="K17" s="15">
-        <v>-37.864077669902</v>
+        <v>-30.088495575221</v>
       </c>
       <c r="L17" s="15">
-        <v>-36.633663366336</v>
+        <v>-28.828828828828</v>
       </c>
       <c r="M17" s="15">
-        <v>20.754716981132</v>
+        <v>27.419354838709</v>
       </c>
       <c r="N17" s="15">
-        <v>-4.477611940298</v>
+        <v>11.267605633802</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="D18" s="14">
+        <v>2</v>
+      </c>
+      <c r="E18" s="15">
+        <v>100</v>
       </c>
       <c r="F18" s="14">
         <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>8.333333333333</v>
+        <v>44.444444444444</v>
       </c>
       <c r="I18" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J18" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K18" s="15">
-        <v>-38.235294117647</v>
+        <v>-30.555555555555</v>
       </c>
       <c r="L18" s="15">
-        <v>-52.272727272727</v>
+        <v>-52.830188679245</v>
       </c>
       <c r="M18" s="15">
-        <v>-64.406779661017</v>
+        <v>-62.686567164179</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.992366412213</v>
+        <v>-95.503597122302</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G19" s="14">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H19" s="15">
-        <v>-29.824561403508</v>
+        <v>-37.5</v>
       </c>
       <c r="I19" s="14">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="J19" s="14">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="K19" s="15">
-        <v>-22.666666666666</v>
+        <v>-23.456790123456</v>
       </c>
       <c r="L19" s="15">
-        <v>-41.414141414141</v>
+        <v>-41.784037558685</v>
       </c>
       <c r="M19" s="15">
-        <v>28.888888888888</v>
+        <v>29.166666666666</v>
       </c>
       <c r="N19" s="15">
-        <v>-52.263374485596</v>
+        <v>-54.411764705882</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F20" s="14">
+        <v>21</v>
+      </c>
+      <c r="G20" s="14">
         <v>23</v>
       </c>
-      <c r="G20" s="14">
-        <v>16</v>
-      </c>
       <c r="H20" s="15">
-        <v>43.75</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="I20" s="14">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J20" s="14">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K20" s="15">
-        <v>25</v>
+        <v>10.638297872340</v>
       </c>
       <c r="L20" s="15">
-        <v>-4.255319148936</v>
+        <v>-8.771929824561</v>
       </c>
       <c r="M20" s="15">
-        <v>-2.173913043478</v>
+        <v>8.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.749430523918</v>
+        <v>-89.233954451345</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,75 +1139,75 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D21" s="17">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E21" s="18">
-        <v>-35.135135135135</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F21" s="17">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G21" s="17">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.516556291390</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="I21" s="17">
-        <v>302</v>
+        <v>340</v>
       </c>
       <c r="J21" s="17">
-        <v>380</v>
+        <v>422</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.526315789473</v>
+        <v>-19.431279620853</v>
       </c>
       <c r="L21" s="18">
-        <v>-35.193133047210</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="M21" s="18">
-        <v>-4.126984126984</v>
+        <v>-0.584795321637</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.440414507772</v>
+        <v>-79.821958456973</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="14">
-        <v>3</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="I22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J22" s="14">
         <v>13</v>
       </c>
       <c r="K22" s="15">
-        <v>-46.153846153846</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="L22" s="15">
-        <v>-56.25</v>
+        <v>-50</v>
       </c>
       <c r="M22" s="15">
         <v>0</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D24" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E24" s="15">
-        <v>4</v>
+        <v>29.629629629629</v>
       </c>
       <c r="F24" s="14">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G24" s="14">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H24" s="15">
-        <v>7.142857142857</v>
+        <v>13</v>
       </c>
       <c r="I24" s="14">
-        <v>235</v>
+        <v>270</v>
       </c>
       <c r="J24" s="14">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="K24" s="15">
-        <v>-13.919413919413</v>
+        <v>-10</v>
       </c>
       <c r="L24" s="15">
-        <v>-54.011741682974</v>
+        <v>-51.263537906137</v>
       </c>
       <c r="M24" s="15">
-        <v>19.897959183673</v>
+        <v>23.853211009174</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>12</v>
+      </c>
+      <c r="D25" s="14">
         <v>11</v>
       </c>
-      <c r="D25" s="14">
-        <v>10</v>
-      </c>
       <c r="E25" s="15">
-        <v>10</v>
+        <v>9.090909090909</v>
       </c>
       <c r="F25" s="14">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G25" s="14">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H25" s="15">
-        <v>-34.146341463414</v>
+        <v>-23.255813953488</v>
       </c>
       <c r="I25" s="14">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="J25" s="14">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="K25" s="15">
-        <v>-55.2</v>
+        <v>-50</v>
       </c>
       <c r="L25" s="15">
-        <v>-81.639344262295</v>
+        <v>-79.393939393939</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>21</v>
+      </c>
+      <c r="D26" s="14">
         <v>24</v>
       </c>
-      <c r="D26" s="14">
-        <v>27</v>
-      </c>
       <c r="E26" s="15">
-        <v>-11.111111111111</v>
+        <v>-12.5</v>
       </c>
       <c r="F26" s="14">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G26" s="14">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="H26" s="15">
-        <v>-27.160493827160</v>
+        <v>-34.736842105263</v>
       </c>
       <c r="I26" s="14">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="J26" s="14">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="K26" s="15">
-        <v>-19.523809523809</v>
+        <v>-20.085470085470</v>
       </c>
       <c r="L26" s="15">
-        <v>-23.873873873873</v>
+        <v>-24.596774193548</v>
       </c>
       <c r="M26" s="15">
-        <v>-8.648648648648</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>3</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>500</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I27" s="14">
         <v>12</v>
       </c>
       <c r="J27" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K27" s="15">
-        <v>50</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L27" s="15">
-        <v>-7.692307692307</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>5</v>
       </c>
       <c r="D28" s="14">
         <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G28" s="14">
         <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="I28" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J28" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K28" s="15">
-        <v>-5.263157894736</v>
+        <v>4.545454545454</v>
       </c>
       <c r="L28" s="15">
-        <v>-35.714285714285</v>
+        <v>-28.125</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-115pct.xlsx
+++ b/data/source/weekly/cs-en-us-115pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -881,8 +881,8 @@
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="15">
+        <v>-100</v>
       </c>
       <c r="N14" s="15">
         <v>-100</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
         <v>3</v>
       </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="14">
+      <c r="G15" s="14">
         <v>4</v>
       </c>
-      <c r="G15" s="14">
-        <v>3</v>
-      </c>
       <c r="H15" s="15">
-        <v>33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="I15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K15" s="15">
         <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>28.571428571428</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M15" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>12.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
+        <v>100</v>
+      </c>
+      <c r="F16" s="14">
+        <v>21</v>
+      </c>
+      <c r="G16" s="14">
+        <v>21</v>
+      </c>
+      <c r="H16" s="15">
         <v>0</v>
       </c>
-      <c r="F16" s="14">
-        <v>14</v>
-      </c>
-      <c r="G16" s="14">
-        <v>21</v>
-      </c>
-      <c r="H16" s="15">
-        <v>-33.333333333333</v>
-      </c>
       <c r="I16" s="14">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J16" s="14">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K16" s="15">
-        <v>-3.773584905660</v>
+        <v>6.896551724137</v>
       </c>
       <c r="L16" s="15">
-        <v>-35.443037974683</v>
+        <v>-28.735632183908</v>
       </c>
       <c r="M16" s="15">
-        <v>-22.727272727272</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.291666666666</v>
+        <v>-80.128205128205</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>30</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F17" s="14">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G17" s="14">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H17" s="15">
-        <v>-25</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="I17" s="14">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J17" s="14">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="K17" s="15">
-        <v>-30.088495575221</v>
+        <v>-29.838709677419</v>
       </c>
       <c r="L17" s="15">
-        <v>-28.828828828828</v>
+        <v>-26.890756302521</v>
       </c>
       <c r="M17" s="15">
-        <v>27.419354838709</v>
+        <v>26.086956521739</v>
       </c>
       <c r="N17" s="15">
-        <v>11.267605633802</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
+        <v>14</v>
+      </c>
+      <c r="G18" s="14">
         <v>13</v>
       </c>
-      <c r="G18" s="14">
-        <v>9</v>
-      </c>
       <c r="H18" s="15">
-        <v>44.444444444444</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I18" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J18" s="14">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="K18" s="15">
-        <v>-30.555555555555</v>
+        <v>-35.555555555555</v>
       </c>
       <c r="L18" s="15">
-        <v>-52.830188679245</v>
+        <v>-50.847457627118</v>
       </c>
       <c r="M18" s="15">
-        <v>-62.686567164179</v>
+        <v>-61.842105263157</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.503597122302</v>
+        <v>-95.198675496688</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>-33.333333333333</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G19" s="14">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H19" s="15">
-        <v>-37.5</v>
+        <v>-36.538461538461</v>
       </c>
       <c r="I19" s="14">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="J19" s="14">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="K19" s="15">
-        <v>-23.456790123456</v>
+        <v>-23.295454545454</v>
       </c>
       <c r="L19" s="15">
-        <v>-41.784037558685</v>
+        <v>-40.528634361233</v>
       </c>
       <c r="M19" s="15">
-        <v>29.166666666666</v>
+        <v>31.067961165048</v>
       </c>
       <c r="N19" s="15">
-        <v>-54.411764705882</v>
+        <v>-53.767123287671</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>-36.363636363636</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G20" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H20" s="15">
-        <v>-8.695652173913</v>
+        <v>-12</v>
       </c>
       <c r="I20" s="14">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J20" s="14">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="K20" s="15">
-        <v>10.638297872340</v>
+        <v>7.547169811320</v>
       </c>
       <c r="L20" s="15">
-        <v>-8.771929824561</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="M20" s="15">
-        <v>8.333333333333</v>
+        <v>-1.724137931034</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.233954451345</v>
+        <v>-89.163498098859</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,45 +1142,45 @@
         <v>36</v>
       </c>
       <c r="D21" s="17">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E21" s="18">
-        <v>-14.285714285714</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="F21" s="17">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G21" s="17">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H21" s="18">
-        <v>-23.076923076923</v>
+        <v>-20.382165605095</v>
       </c>
       <c r="I21" s="17">
-        <v>340</v>
+        <v>380</v>
       </c>
       <c r="J21" s="17">
-        <v>422</v>
+        <v>468</v>
       </c>
       <c r="K21" s="18">
-        <v>-19.431279620853</v>
+        <v>-18.803418803418</v>
       </c>
       <c r="L21" s="18">
-        <v>-34.615384615384</v>
+        <v>-32.384341637010</v>
       </c>
       <c r="M21" s="18">
-        <v>-0.584795321637</v>
+        <v>-0.523560209424</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.821958456973</v>
+        <v>-79.166666666666</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1207,10 +1207,10 @@
         <v>-38.461538461538</v>
       </c>
       <c r="L22" s="15">
-        <v>-50</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E24" s="15">
-        <v>29.629629629629</v>
+        <v>-28.125</v>
       </c>
       <c r="F24" s="14">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G24" s="14">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H24" s="15">
-        <v>13</v>
+        <v>1.904761904761</v>
       </c>
       <c r="I24" s="14">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="J24" s="14">
-        <v>300</v>
+        <v>332</v>
       </c>
       <c r="K24" s="15">
-        <v>-10</v>
+        <v>-12.349397590361</v>
       </c>
       <c r="L24" s="15">
-        <v>-51.263537906137</v>
+        <v>-52.059308072487</v>
       </c>
       <c r="M24" s="15">
-        <v>23.853211009174</v>
+        <v>24.892703862660</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E25" s="15">
-        <v>9.090909090909</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F25" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G25" s="14">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H25" s="15">
-        <v>-23.255813953488</v>
+        <v>-15.909090909090</v>
       </c>
       <c r="I25" s="14">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J25" s="14">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="K25" s="15">
-        <v>-50</v>
+        <v>-48.993288590604</v>
       </c>
       <c r="L25" s="15">
-        <v>-79.393939393939</v>
+        <v>-78.830083565459</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E26" s="15">
-        <v>-12.5</v>
+        <v>-30</v>
       </c>
       <c r="F26" s="14">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G26" s="14">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="H26" s="15">
-        <v>-34.736842105263</v>
+        <v>-35.643564356435</v>
       </c>
       <c r="I26" s="14">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="J26" s="14">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="K26" s="15">
-        <v>-20.085470085470</v>
+        <v>-21.653543307086</v>
       </c>
       <c r="L26" s="15">
-        <v>-24.596774193548</v>
+        <v>-26.568265682656</v>
       </c>
       <c r="M26" s="15">
-        <v>-8.333333333333</v>
+        <v>-10.762331838565</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
+      </c>
+      <c r="F27" s="14">
         <v>3</v>
       </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="14">
+      <c r="G27" s="14">
         <v>4</v>
       </c>
-      <c r="G27" s="14">
-        <v>3</v>
-      </c>
       <c r="H27" s="15">
-        <v>33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="I27" s="14">
+        <v>13</v>
+      </c>
+      <c r="J27" s="14">
         <v>12</v>
       </c>
-      <c r="J27" s="14">
-        <v>11</v>
-      </c>
       <c r="K27" s="15">
-        <v>9.090909090909</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>-14.285714285714</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
         <v>12</v>
       </c>
       <c r="G28" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H28" s="15">
-        <v>20</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J28" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K28" s="15">
-        <v>4.545454545454</v>
+        <v>12.5</v>
       </c>
       <c r="L28" s="15">
-        <v>-28.125</v>
+        <v>-25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>200</v>
       </c>
       <c r="L31" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1619,11 +1619,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-115pct.xlsx
+++ b/data/source/weekly/cs-en-us-115pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -869,37 +869,37 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="14">
         <v>2</v>
       </c>
       <c r="K14" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M14" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-100</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>3</v>
@@ -920,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>42.857142857142</v>
+        <v>25</v>
       </c>
       <c r="M15" s="15">
         <v>100</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>6</v>
+      </c>
+      <c r="D16" s="14">
         <v>10</v>
       </c>
-      <c r="D16" s="14">
-        <v>5</v>
-      </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>-40</v>
       </c>
       <c r="F16" s="14">
         <v>21</v>
       </c>
       <c r="G16" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H16" s="15">
+        <v>-16</v>
+      </c>
+      <c r="I16" s="14">
+        <v>68</v>
+      </c>
+      <c r="J16" s="14">
+        <v>68</v>
+      </c>
+      <c r="K16" s="15">
         <v>0</v>
       </c>
-      <c r="I16" s="14">
-        <v>62</v>
-      </c>
-      <c r="J16" s="14">
-        <v>58</v>
-      </c>
-      <c r="K16" s="15">
-        <v>6.896551724137</v>
-      </c>
       <c r="L16" s="15">
-        <v>-28.735632183908</v>
+        <v>-28.421052631578</v>
       </c>
       <c r="M16" s="15">
-        <v>-11.428571428571</v>
+        <v>-16.049382716049</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.128205128205</v>
+        <v>-79.518072289156</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>-45.454545454545</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
         <v>32</v>
       </c>
       <c r="G17" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H17" s="15">
-        <v>-23.809523809523</v>
+        <v>-28.888888888888</v>
       </c>
       <c r="I17" s="14">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="J17" s="14">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K17" s="15">
-        <v>-29.838709677419</v>
+        <v>-30.075187969924</v>
       </c>
       <c r="L17" s="15">
-        <v>-26.890756302521</v>
+        <v>-29.007633587786</v>
       </c>
       <c r="M17" s="15">
-        <v>26.086956521739</v>
+        <v>22.368421052631</v>
       </c>
       <c r="N17" s="15">
-        <v>16</v>
+        <v>13.414634146341</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>7.692307692307</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="I18" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J18" s="14">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="K18" s="15">
-        <v>-35.555555555555</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="L18" s="15">
-        <v>-50.847457627118</v>
+        <v>-51.612903225806</v>
       </c>
       <c r="M18" s="15">
-        <v>-61.842105263157</v>
+        <v>-62.5</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.198675496688</v>
+        <v>-95.253164556962</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>-14.285714285714</v>
+        <v>81.818181818181</v>
       </c>
       <c r="F19" s="14">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G19" s="14">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H19" s="15">
-        <v>-36.538461538461</v>
+        <v>-6.382978723404</v>
       </c>
       <c r="I19" s="14">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="J19" s="14">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="K19" s="15">
-        <v>-23.295454545454</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="L19" s="15">
-        <v>-40.528634361233</v>
+        <v>-37.142857142857</v>
       </c>
       <c r="M19" s="15">
-        <v>31.067961165048</v>
+        <v>38.738738738738</v>
       </c>
       <c r="N19" s="15">
-        <v>-53.767123287671</v>
+        <v>-51.724137931034</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
         <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>-33.333333333333</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G20" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H20" s="15">
-        <v>-12</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="I20" s="14">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J20" s="14">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K20" s="15">
-        <v>7.547169811320</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-9.523809523809</v>
+        <v>-18.055555555555</v>
       </c>
       <c r="M20" s="15">
-        <v>-1.724137931034</v>
+        <v>-1.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.163498098859</v>
+        <v>-89.575971731448</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D21" s="17">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E21" s="18">
-        <v>-21.739130434782</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G21" s="17">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="H21" s="18">
-        <v>-20.382165605095</v>
+        <v>-20.359281437125</v>
       </c>
       <c r="I21" s="17">
-        <v>380</v>
+        <v>415</v>
       </c>
       <c r="J21" s="17">
-        <v>468</v>
+        <v>510</v>
       </c>
       <c r="K21" s="18">
-        <v>-18.803418803418</v>
+        <v>-18.627450980392</v>
       </c>
       <c r="L21" s="18">
-        <v>-32.384341637010</v>
+        <v>-32.300163132137</v>
       </c>
       <c r="M21" s="18">
-        <v>-0.523560209424</v>
+        <v>0.241545893719</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.166666666666</v>
+        <v>-78.674203494347</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>3</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H22" s="15">
-        <v>-75</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I22" s="14">
         <v>8</v>
       </c>
       <c r="J22" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K22" s="15">
-        <v>-38.461538461538</v>
+        <v>-50</v>
       </c>
       <c r="L22" s="15">
-        <v>-52.941176470588</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M22" s="15">
-        <v>-11.111111111111</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>-28.125</v>
+        <v>52.941176470588</v>
       </c>
       <c r="F24" s="14">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G24" s="14">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H24" s="15">
-        <v>1.904761904761</v>
+        <v>7.920792079207</v>
       </c>
       <c r="I24" s="14">
-        <v>291</v>
+        <v>318</v>
       </c>
       <c r="J24" s="14">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="K24" s="15">
-        <v>-12.349397590361</v>
+        <v>-8.882521489971</v>
       </c>
       <c r="L24" s="15">
-        <v>-52.059308072487</v>
+        <v>-51.671732522796</v>
       </c>
       <c r="M24" s="15">
-        <v>24.892703862660</v>
+        <v>30.864197530864</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>-38.461538461538</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G25" s="14">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H25" s="15">
-        <v>-15.909090909090</v>
+        <v>-7.317073170731</v>
       </c>
       <c r="I25" s="14">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J25" s="14">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="K25" s="15">
-        <v>-48.993288590604</v>
+        <v>-46.794871794871</v>
       </c>
       <c r="L25" s="15">
-        <v>-78.830083565459</v>
+        <v>-78.552971576227</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D26" s="14">
         <v>20</v>
       </c>
       <c r="E26" s="15">
-        <v>-30</v>
+        <v>20</v>
       </c>
       <c r="F26" s="14">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="G26" s="14">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="H26" s="15">
-        <v>-35.643564356435</v>
+        <v>-10.989010989011</v>
       </c>
       <c r="I26" s="14">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="J26" s="14">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="K26" s="15">
-        <v>-21.653543307086</v>
+        <v>-18.978102189781</v>
       </c>
       <c r="L26" s="15">
-        <v>-26.568265682656</v>
+        <v>-23.183391003460</v>
       </c>
       <c r="M26" s="15">
-        <v>-10.762331838565</v>
+        <v>-9.016393442622</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
         <v>13</v>
       </c>
       <c r="J27" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K27" s="15">
-        <v>8.333333333333</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L27" s="15">
-        <v>-13.333333333333</v>
+        <v>-18.75</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J28" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K28" s="15">
-        <v>12.5</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L28" s="15">
-        <v>-25</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,8 +1484,8 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="14">
+        <v>1</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1497,18 +1497,18 @@
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,8 +1525,8 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1538,10 +1538,10 @@
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1567,16 +1567,16 @@
         <v>-100</v>
       </c>
       <c r="I31" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J31" s="14">
         <v>1</v>
       </c>
       <c r="K31" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L31" s="15">
-        <v>-40</v>
+        <v>-60</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-115pct.xlsx
+++ b/data/source/weekly/cs-en-us-115pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J15" s="14">
         <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L15" s="15">
-        <v>25</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="N15" s="15">
-        <v>25</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>-40</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F16" s="14">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G16" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H16" s="15">
-        <v>-16</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="I16" s="14">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="J16" s="14">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="K16" s="15">
-        <v>0</v>
+        <v>-2.597402597402</v>
       </c>
       <c r="L16" s="15">
-        <v>-28.421052631578</v>
+        <v>-27.184466019417</v>
       </c>
       <c r="M16" s="15">
-        <v>-16.049382716049</v>
+        <v>-17.582417582417</v>
       </c>
       <c r="N16" s="15">
-        <v>-79.518072289156</v>
+        <v>-78.813559322033</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>-12.5</v>
       </c>
       <c r="F17" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G17" s="14">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H17" s="15">
-        <v>-28.888888888888</v>
+        <v>-7.894736842105</v>
       </c>
       <c r="I17" s="14">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="J17" s="14">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="K17" s="15">
-        <v>-30.075187969924</v>
+        <v>-28.368794326241</v>
       </c>
       <c r="L17" s="15">
-        <v>-29.007633587786</v>
+        <v>-27.857142857142</v>
       </c>
       <c r="M17" s="15">
-        <v>22.368421052631</v>
+        <v>21.686746987951</v>
       </c>
       <c r="N17" s="15">
-        <v>13.414634146341</v>
+        <v>9.782608695652</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-83.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>-23.529411764705</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J18" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K18" s="15">
-        <v>-41.176470588235</v>
+        <v>-38.181818181818</v>
       </c>
       <c r="L18" s="15">
-        <v>-51.612903225806</v>
+        <v>-47.692307692307</v>
       </c>
       <c r="M18" s="15">
-        <v>-62.5</v>
+        <v>-59.523809523809</v>
       </c>
       <c r="N18" s="15">
-        <v>-95.253164556962</v>
+        <v>-94.894894894894</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>81.818181818181</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F19" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G19" s="14">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H19" s="15">
-        <v>-6.382978723404</v>
+        <v>-3.921568627450</v>
       </c>
       <c r="I19" s="14">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="J19" s="14">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="K19" s="15">
-        <v>-17.647058823529</v>
+        <v>-18.407960199005</v>
       </c>
       <c r="L19" s="15">
-        <v>-37.142857142857</v>
+        <v>-36.923076923076</v>
       </c>
       <c r="M19" s="15">
-        <v>38.738738738738</v>
+        <v>36.666666666666</v>
       </c>
       <c r="N19" s="15">
-        <v>-51.724137931034</v>
+        <v>-52.046783625731</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-83.333333333333</v>
+        <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G20" s="14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H20" s="15">
-        <v>-34.482758620689</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I20" s="14">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="J20" s="14">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>9.677419354838</v>
       </c>
       <c r="L20" s="15">
-        <v>-18.055555555555</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="M20" s="15">
-        <v>-1.666666666666</v>
+        <v>7.936507936507</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.575971731448</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D21" s="17">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E21" s="18">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="G21" s="17">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H21" s="18">
-        <v>-20.359281437125</v>
+        <v>-11.904761904761</v>
       </c>
       <c r="I21" s="17">
-        <v>415</v>
+        <v>454</v>
       </c>
       <c r="J21" s="17">
-        <v>510</v>
+        <v>548</v>
       </c>
       <c r="K21" s="18">
-        <v>-18.627450980392</v>
+        <v>-17.153284671532</v>
       </c>
       <c r="L21" s="18">
-        <v>-32.300163132137</v>
+        <v>-30.474732006125</v>
       </c>
       <c r="M21" s="18">
-        <v>0.241545893719</v>
+        <v>1.565995525727</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.674203494347</v>
+        <v>-78.183565593464</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,7 +1183,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
         <v>-100</v>
@@ -1192,22 +1192,22 @@
         <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-83.333333333333</v>
+        <v>-80</v>
       </c>
       <c r="I22" s="14">
         <v>8</v>
       </c>
       <c r="J22" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K22" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L22" s="15">
-        <v>-55.555555555555</v>
+        <v>-60</v>
       </c>
       <c r="M22" s="15">
         <v>-27.272727272727</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E24" s="15">
-        <v>52.941176470588</v>
+        <v>-28</v>
       </c>
       <c r="F24" s="14">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="G24" s="14">
         <v>101</v>
       </c>
       <c r="H24" s="15">
-        <v>7.920792079207</v>
+        <v>0.990099009900</v>
       </c>
       <c r="I24" s="14">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="J24" s="14">
-        <v>349</v>
+        <v>374</v>
       </c>
       <c r="K24" s="15">
-        <v>-8.882521489971</v>
+        <v>-9.625668449197</v>
       </c>
       <c r="L24" s="15">
-        <v>-51.671732522796</v>
+        <v>-51.506456241033</v>
       </c>
       <c r="M24" s="15">
-        <v>30.864197530864</v>
+        <v>25.650557620817</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="F25" s="14">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G25" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H25" s="15">
-        <v>-7.317073170731</v>
+        <v>-26.190476190476</v>
       </c>
       <c r="I25" s="14">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J25" s="14">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="K25" s="15">
-        <v>-46.794871794871</v>
+        <v>-47.904191616766</v>
       </c>
       <c r="L25" s="15">
-        <v>-78.552971576227</v>
+        <v>-78.465346534653</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D26" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E26" s="15">
-        <v>20</v>
+        <v>56.25</v>
       </c>
       <c r="F26" s="14">
         <v>81</v>
       </c>
       <c r="G26" s="14">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H26" s="15">
-        <v>-10.989010989011</v>
+        <v>1.25</v>
       </c>
       <c r="I26" s="14">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="J26" s="14">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="K26" s="15">
-        <v>-18.978102189781</v>
+        <v>-15.172413793103</v>
       </c>
       <c r="L26" s="15">
-        <v>-23.183391003460</v>
+        <v>-21.656050955414</v>
       </c>
       <c r="M26" s="15">
-        <v>-9.016393442622</v>
+        <v>-5.747126436781</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="14">
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>3</v>
       </c>
       <c r="G27" s="14">
         <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J27" s="14">
         <v>14</v>
       </c>
       <c r="K27" s="15">
-        <v>-7.142857142857</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-18.75</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G28" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>44.444444444444</v>
       </c>
       <c r="I28" s="14">
+        <v>31</v>
+      </c>
+      <c r="J28" s="14">
         <v>28</v>
       </c>
-      <c r="J28" s="14">
-        <v>26</v>
-      </c>
       <c r="K28" s="15">
-        <v>7.692307692307</v>
+        <v>10.714285714285</v>
       </c>
       <c r="L28" s="15">
-        <v>-26.315789473684</v>
+        <v>-26.190476190476</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-115pct.xlsx
+++ b/data/source/weekly/cs-en-us-115pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -854,29 +854,29 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>0</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
       </c>
       <c r="J14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,10 +905,10 @@
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
         <v>11</v>
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="L15" s="15">
-        <v>22.222222222222</v>
+        <v>10</v>
       </c>
       <c r="M15" s="15">
         <v>120</v>
       </c>
       <c r="N15" s="15">
-        <v>37.5</v>
+        <v>22.222222222222</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>-22.222222222222</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
         <v>27</v>
       </c>
       <c r="G16" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H16" s="15">
-        <v>-3.571428571428</v>
+        <v>-10</v>
       </c>
       <c r="I16" s="14">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J16" s="14">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K16" s="15">
-        <v>-2.597402597402</v>
+        <v>-3.614457831325</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.184466019417</v>
+        <v>-27.927927927927</v>
       </c>
       <c r="M16" s="15">
-        <v>-17.582417582417</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-78.813559322033</v>
+        <v>-78.947368421052</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E17" s="15">
-        <v>-12.5</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="F17" s="14">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G17" s="14">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H17" s="15">
-        <v>-7.894736842105</v>
+        <v>-37.777777777777</v>
       </c>
       <c r="I17" s="14">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="J17" s="14">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="K17" s="15">
-        <v>-28.368794326241</v>
+        <v>-31.012658227848</v>
       </c>
       <c r="L17" s="15">
-        <v>-27.857142857142</v>
+        <v>-31.875</v>
       </c>
       <c r="M17" s="15">
-        <v>21.686746987951</v>
+        <v>18.478260869565</v>
       </c>
       <c r="N17" s="15">
-        <v>9.782608695652</v>
+        <v>2.830188679245</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1028,28 +1028,28 @@
         <v>12</v>
       </c>
       <c r="G18" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H18" s="15">
-        <v>-42.857142857142</v>
+        <v>-47.826086956521</v>
       </c>
       <c r="I18" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J18" s="14">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K18" s="15">
-        <v>-38.181818181818</v>
+        <v>-33.898305084745</v>
       </c>
       <c r="L18" s="15">
-        <v>-47.692307692307</v>
+        <v>-40</v>
       </c>
       <c r="M18" s="15">
-        <v>-59.523809523809</v>
+        <v>-59.375</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.894894894894</v>
+        <v>-94.483734087694</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>-28.571428571428</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F19" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G19" s="14">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H19" s="15">
-        <v>-3.921568627450</v>
+        <v>-8.771929824561</v>
       </c>
       <c r="I19" s="14">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="J19" s="14">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="K19" s="15">
-        <v>-18.407960199005</v>
+        <v>-20.547945205479</v>
       </c>
       <c r="L19" s="15">
-        <v>-36.923076923076</v>
+        <v>-36.727272727272</v>
       </c>
       <c r="M19" s="15">
-        <v>36.666666666666</v>
+        <v>40.322580645161</v>
       </c>
       <c r="N19" s="15">
-        <v>-52.046783625731</v>
+        <v>-52.459016393442</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="F20" s="14">
         <v>22</v>
       </c>
       <c r="G20" s="14">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H20" s="15">
-        <v>-15.384615384615</v>
+        <v>10</v>
       </c>
       <c r="I20" s="14">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="J20" s="14">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K20" s="15">
-        <v>9.677419354838</v>
+        <v>11.940298507462</v>
       </c>
       <c r="L20" s="15">
-        <v>-10.526315789473</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="M20" s="15">
-        <v>7.936507936507</v>
+        <v>17.1875</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.888888888888</v>
+        <v>-88.653555219364</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D21" s="17">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G21" s="17">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.904761904761</v>
+        <v>-18.644067796610</v>
       </c>
       <c r="I21" s="17">
-        <v>454</v>
+        <v>489</v>
       </c>
       <c r="J21" s="17">
-        <v>548</v>
+        <v>599</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.153284671532</v>
+        <v>-18.363939899833</v>
       </c>
       <c r="L21" s="18">
-        <v>-30.474732006125</v>
+        <v>-30.638297872340</v>
       </c>
       <c r="M21" s="18">
-        <v>1.565995525727</v>
+        <v>2.301255230125</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.183565593464</v>
+        <v>-78.130590339892</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="14">
         <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H22" s="15">
-        <v>-80</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="I22" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J22" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K22" s="15">
-        <v>-55.555555555555</v>
+        <v>-55</v>
       </c>
       <c r="L22" s="15">
-        <v>-60</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M22" s="15">
-        <v>-27.272727272727</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E24" s="15">
-        <v>-28</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="G24" s="14">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H24" s="15">
-        <v>0.990099009900</v>
+        <v>-10.576923076923</v>
       </c>
       <c r="I24" s="14">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="J24" s="14">
-        <v>374</v>
+        <v>404</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.625668449197</v>
+        <v>-10.396039603960</v>
       </c>
       <c r="L24" s="15">
-        <v>-51.506456241033</v>
+        <v>-50.748299319727</v>
       </c>
       <c r="M24" s="15">
-        <v>25.650557620817</v>
+        <v>23.129251700680</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>-63.636363636363</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F25" s="14">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G25" s="14">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H25" s="15">
-        <v>-26.190476190476</v>
+        <v>-32.5</v>
       </c>
       <c r="I25" s="14">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="J25" s="14">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="K25" s="15">
-        <v>-47.904191616766</v>
+        <v>-46.022727272727</v>
       </c>
       <c r="L25" s="15">
-        <v>-78.465346534653</v>
+        <v>-77.751756440281</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E26" s="15">
-        <v>56.25</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="F26" s="14">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G26" s="14">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H26" s="15">
-        <v>1.25</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="I26" s="14">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="J26" s="14">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="K26" s="15">
-        <v>-15.172413793103</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L26" s="15">
-        <v>-21.656050955414</v>
+        <v>-24.418604651162</v>
       </c>
       <c r="M26" s="15">
-        <v>-5.747126436781</v>
+        <v>-7.801418439716</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>100</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J27" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>6.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>-22.222222222222</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G28" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>44.444444444444</v>
+        <v>37.5</v>
       </c>
       <c r="I28" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J28" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K28" s="15">
-        <v>10.714285714285</v>
+        <v>10</v>
       </c>
       <c r="L28" s="15">
-        <v>-26.190476190476</v>
+        <v>-23.255813953488</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-92.857142857142</v>
+        <v>-93.75</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.307692307692</v>
+        <v>-93.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,17 +1551,17 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
         <v>-100</v>
@@ -1570,10 +1570,10 @@
         <v>2</v>
       </c>
       <c r="J31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L31" s="15">
         <v>-60</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="L33" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-115pct.xlsx
+++ b/data/source/weekly/cs-en-us-115pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-50</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J15" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M15" s="15">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="N15" s="15">
-        <v>22.222222222222</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G16" s="14">
         <v>30</v>
       </c>
       <c r="H16" s="15">
-        <v>-10</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J16" s="14">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="K16" s="15">
-        <v>-3.614457831325</v>
+        <v>-3.409090909090</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.927927927927</v>
+        <v>-27.350427350427</v>
       </c>
       <c r="M16" s="15">
         <v>-16.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-78.947368421052</v>
+        <v>-78.855721393034</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
         <v>17</v>
       </c>
       <c r="E17" s="15">
-        <v>-47.058823529411</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="F17" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G17" s="14">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H17" s="15">
-        <v>-37.777777777777</v>
+        <v>-43.137254901960</v>
       </c>
       <c r="I17" s="14">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="J17" s="14">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="K17" s="15">
-        <v>-31.012658227848</v>
+        <v>-33.714285714285</v>
       </c>
       <c r="L17" s="15">
-        <v>-31.875</v>
+        <v>-29.696969696969</v>
       </c>
       <c r="M17" s="15">
-        <v>18.478260869565</v>
+        <v>19.587628865979</v>
       </c>
       <c r="N17" s="15">
-        <v>2.830188679245</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F18" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>-47.826086956521</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="I18" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J18" s="14">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K18" s="15">
-        <v>-33.898305084745</v>
+        <v>-32.8125</v>
       </c>
       <c r="L18" s="15">
-        <v>-40</v>
+        <v>-39.436619718309</v>
       </c>
       <c r="M18" s="15">
-        <v>-59.375</v>
+        <v>-57.843137254902</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.483734087694</v>
+        <v>-94.141689373297</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>17</v>
+      </c>
+      <c r="D19" s="14">
         <v>10</v>
       </c>
-      <c r="D19" s="14">
-        <v>18</v>
-      </c>
       <c r="E19" s="15">
-        <v>-44.444444444444</v>
+        <v>70</v>
       </c>
       <c r="F19" s="14">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G19" s="14">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H19" s="15">
-        <v>-8.771929824561</v>
+        <v>7.547169811320</v>
       </c>
       <c r="I19" s="14">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="J19" s="14">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="K19" s="15">
-        <v>-20.547945205479</v>
+        <v>-16.157205240174</v>
       </c>
       <c r="L19" s="15">
-        <v>-36.727272727272</v>
+        <v>-34.246575342465</v>
       </c>
       <c r="M19" s="15">
-        <v>40.322580645161</v>
+        <v>47.692307692307</v>
       </c>
       <c r="N19" s="15">
-        <v>-52.459016393442</v>
+        <v>-50.259067357513</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G20" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H20" s="15">
-        <v>10</v>
+        <v>43.75</v>
       </c>
       <c r="I20" s="14">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="J20" s="14">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K20" s="15">
-        <v>11.940298507462</v>
+        <v>17.391304347826</v>
       </c>
       <c r="L20" s="15">
-        <v>-10.714285714285</v>
+        <v>-7.954545454545</v>
       </c>
       <c r="M20" s="15">
-        <v>17.1875</v>
+        <v>19.117647058823</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.653555219364</v>
+        <v>-88.477951635846</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D21" s="17">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E21" s="18">
-        <v>-33.333333333333</v>
+        <v>-2.439024390243</v>
       </c>
       <c r="F21" s="17">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G21" s="17">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H21" s="18">
-        <v>-18.644067796610</v>
+        <v>-14.534883720930</v>
       </c>
       <c r="I21" s="17">
-        <v>489</v>
+        <v>530</v>
       </c>
       <c r="J21" s="17">
-        <v>599</v>
+        <v>640</v>
       </c>
       <c r="K21" s="18">
-        <v>-18.363939899833</v>
+        <v>-17.1875</v>
       </c>
       <c r="L21" s="18">
-        <v>-30.638297872340</v>
+        <v>-28.667563930013</v>
       </c>
       <c r="M21" s="18">
-        <v>2.301255230125</v>
+        <v>4.950495049504</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.130590339892</v>
+        <v>-77.523324851569</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
-      </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-50</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
@@ -1210,7 +1210,7 @@
         <v>-57.142857142857</v>
       </c>
       <c r="M22" s="15">
-        <v>-18.181818181818</v>
+        <v>-25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>-16.666666666666</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G24" s="14">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="H24" s="15">
-        <v>-10.576923076923</v>
+        <v>1.111111111111</v>
       </c>
       <c r="I24" s="14">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="J24" s="14">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="K24" s="15">
-        <v>-10.396039603960</v>
+        <v>-9.478672985781</v>
       </c>
       <c r="L24" s="15">
-        <v>-50.748299319727</v>
+        <v>-50.773195876288</v>
       </c>
       <c r="M24" s="15">
-        <v>23.129251700680</v>
+        <v>19.375</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
         <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>-11.111111111111</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F25" s="14">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G25" s="14">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H25" s="15">
-        <v>-32.5</v>
+        <v>-36.111111111111</v>
       </c>
       <c r="I25" s="14">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J25" s="14">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="K25" s="15">
-        <v>-46.022727272727</v>
+        <v>-46.486486486486</v>
       </c>
       <c r="L25" s="15">
-        <v>-77.751756440281</v>
+        <v>-77.951002227171</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E26" s="15">
-        <v>-40.909090909090</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F26" s="14">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G26" s="14">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H26" s="15">
-        <v>-3.846153846153</v>
+        <v>-12.658227848101</v>
       </c>
       <c r="I26" s="14">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="J26" s="14">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="K26" s="15">
-        <v>-16.666666666666</v>
+        <v>-19.819819819819</v>
       </c>
       <c r="L26" s="15">
-        <v>-24.418604651162</v>
+        <v>-28.609625668449</v>
       </c>
       <c r="M26" s="15">
-        <v>-7.801418439716</v>
+        <v>-11.589403973509</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
         <v>2</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
       <c r="E27" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
         <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
+        <v>-20</v>
+      </c>
+      <c r="I27" s="14">
+        <v>17</v>
+      </c>
+      <c r="J27" s="14">
+        <v>17</v>
+      </c>
+      <c r="K27" s="15">
         <v>0</v>
       </c>
-      <c r="I27" s="14">
-        <v>16</v>
-      </c>
-      <c r="J27" s="14">
-        <v>15</v>
-      </c>
-      <c r="K27" s="15">
-        <v>6.666666666666</v>
-      </c>
       <c r="L27" s="15">
-        <v>-15.789473684210</v>
+        <v>-15</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,13 +1426,13 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F28" s="14">
         <v>11</v>
@@ -1444,16 +1444,16 @@
         <v>37.5</v>
       </c>
       <c r="I28" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J28" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K28" s="15">
-        <v>10</v>
+        <v>18.75</v>
       </c>
       <c r="L28" s="15">
-        <v>-23.255813953488</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,17 +1551,17 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="14">
         <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" s="14">
-        <v>2</v>
       </c>
       <c r="H31" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-115pct.xlsx
+++ b/data/source/weekly/cs-en-us-115pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -860,14 +860,14 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="14">
         <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -896,37 +896,37 @@
         <v>1</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J15" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K15" s="15">
         <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M15" s="15">
-        <v>140</v>
+        <v>116.666666666667</v>
       </c>
       <c r="N15" s="15">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-37.5</v>
       </c>
       <c r="F16" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G16" s="14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H16" s="15">
-        <v>-26.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="I16" s="14">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J16" s="14">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="K16" s="15">
-        <v>-3.409090909090</v>
+        <v>-6.25</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.350427350427</v>
+        <v>-27.419354838709</v>
       </c>
       <c r="M16" s="15">
-        <v>-16.666666666666</v>
+        <v>-17.431192660550</v>
       </c>
       <c r="N16" s="15">
-        <v>-78.855721393034</v>
+        <v>-79.020979020979</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15">
-        <v>-58.823529411764</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G17" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H17" s="15">
-        <v>-43.137254901960</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I17" s="14">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="J17" s="14">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="K17" s="15">
-        <v>-33.714285714285</v>
+        <v>-34.224598930481</v>
       </c>
       <c r="L17" s="15">
-        <v>-29.696969696969</v>
+        <v>-32.044198895027</v>
       </c>
       <c r="M17" s="15">
-        <v>19.587628865979</v>
+        <v>20.588235294117</v>
       </c>
       <c r="N17" s="15">
-        <v>0</v>
+        <v>1.652892561983</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>-31.578947368421</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J18" s="14">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K18" s="15">
-        <v>-32.8125</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="L18" s="15">
-        <v>-39.436619718309</v>
+        <v>-39.189189189189</v>
       </c>
       <c r="M18" s="15">
-        <v>-57.843137254902</v>
+        <v>-60.176991150442</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.141689373297</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F19" s="14">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G19" s="14">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H19" s="15">
-        <v>7.547169811320</v>
+        <v>6</v>
       </c>
       <c r="I19" s="14">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="J19" s="14">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="K19" s="15">
-        <v>-16.157205240174</v>
+        <v>-11.814345991561</v>
       </c>
       <c r="L19" s="15">
-        <v>-34.246575342465</v>
+        <v>-31.921824104234</v>
       </c>
       <c r="M19" s="15">
-        <v>47.692307692307</v>
+        <v>50.359712230215</v>
       </c>
       <c r="N19" s="15">
-        <v>-50.259067357513</v>
+        <v>-48.774509803921</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>200</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F20" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G20" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>43.75</v>
+        <v>52.941176470588</v>
       </c>
       <c r="I20" s="14">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J20" s="14">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K20" s="15">
-        <v>17.391304347826</v>
+        <v>11.842105263157</v>
       </c>
       <c r="L20" s="15">
-        <v>-7.954545454545</v>
+        <v>-9.574468085106</v>
       </c>
       <c r="M20" s="15">
-        <v>19.117647058823</v>
+        <v>16.438356164383</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.477951635846</v>
+        <v>-88.666666666666</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D21" s="17">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E21" s="18">
-        <v>-2.439024390243</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="F21" s="17">
         <v>147</v>
       </c>
       <c r="G21" s="17">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.534883720930</v>
+        <v>-12.5</v>
       </c>
       <c r="I21" s="17">
-        <v>530</v>
+        <v>566</v>
       </c>
       <c r="J21" s="17">
-        <v>640</v>
+        <v>678</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.1875</v>
+        <v>-16.519174041297</v>
       </c>
       <c r="L21" s="18">
-        <v>-28.667563930013</v>
+        <v>-28.354430379746</v>
       </c>
       <c r="M21" s="18">
-        <v>4.950495049504</v>
+        <v>4.235727440147</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.523324851569</v>
+        <v>-77.269076305220</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>100</v>
       </c>
       <c r="F22" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-85.714285714285</v>
+        <v>-40</v>
       </c>
       <c r="I22" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J22" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K22" s="15">
-        <v>-55</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="L22" s="15">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
       <c r="M22" s="15">
-        <v>-25</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>16.666666666666</v>
+        <v>21.052631578947</v>
       </c>
       <c r="F24" s="14">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G24" s="14">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H24" s="15">
-        <v>1.111111111111</v>
+        <v>-5.434782608695</v>
       </c>
       <c r="I24" s="14">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="J24" s="14">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.478672985781</v>
+        <v>-8.163265306122</v>
       </c>
       <c r="L24" s="15">
-        <v>-50.773195876288</v>
+        <v>-50.549450549450</v>
       </c>
       <c r="M24" s="15">
-        <v>19.375</v>
+        <v>17.732558139534</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>-55.555555555555</v>
+        <v>100</v>
       </c>
       <c r="F25" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G25" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H25" s="15">
-        <v>-36.111111111111</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="I25" s="14">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="J25" s="14">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K25" s="15">
-        <v>-46.486486486486</v>
+        <v>-42.631578947368</v>
       </c>
       <c r="L25" s="15">
-        <v>-77.951002227171</v>
+        <v>-76.857749469214</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E26" s="15">
-        <v>-71.428571428571</v>
+        <v>-62.5</v>
       </c>
       <c r="F26" s="14">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="G26" s="14">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H26" s="15">
+        <v>-34.939759036144</v>
+      </c>
+      <c r="I26" s="14">
+        <v>276</v>
+      </c>
+      <c r="J26" s="14">
+        <v>357</v>
+      </c>
+      <c r="K26" s="15">
+        <v>-22.689075630252</v>
+      </c>
+      <c r="L26" s="15">
+        <v>-31.343283582089</v>
+      </c>
+      <c r="M26" s="15">
         <v>-12.658227848101</v>
-      </c>
-      <c r="I26" s="14">
-        <v>267</v>
-      </c>
-      <c r="J26" s="14">
-        <v>333</v>
-      </c>
-      <c r="K26" s="15">
-        <v>-19.819819819819</v>
-      </c>
-      <c r="L26" s="15">
-        <v>-28.609625668449</v>
-      </c>
-      <c r="M26" s="15">
-        <v>-11.589403973509</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
+        <v>5</v>
+      </c>
+      <c r="G27" s="14">
         <v>4</v>
       </c>
-      <c r="G27" s="14">
-        <v>5</v>
-      </c>
       <c r="H27" s="15">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="I27" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J27" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K27" s="15">
         <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-15</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
         <v>5</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
       <c r="E28" s="15">
-        <v>150</v>
+        <v>-80</v>
       </c>
       <c r="F28" s="14">
         <v>11</v>
       </c>
       <c r="G28" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H28" s="15">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J28" s="14">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K28" s="15">
-        <v>18.75</v>
+        <v>5.405405405405</v>
       </c>
       <c r="L28" s="15">
-        <v>-20.833333333333</v>
+        <v>-22</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1500,7 +1500,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-93.75</v>
+        <v>-94.444444444444</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-93.333333333333</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1626,16 +1626,16 @@
         <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="14">
         <v>1</v>
       </c>
       <c r="K33" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-115pct.xlsx
+++ b/data/source/weekly/cs-en-us-115pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,17 +854,17 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -873,10 +873,10 @@
         <v>1</v>
       </c>
       <c r="J14" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="I15" s="14">
         <v>13</v>
       </c>
       <c r="J15" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>30</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M15" s="15">
         <v>116.666666666667</v>
       </c>
       <c r="N15" s="15">
-        <v>30</v>
+        <v>18.181818181818</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>-37.5</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G16" s="14">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H16" s="15">
-        <v>-25</v>
+        <v>-28</v>
       </c>
       <c r="I16" s="14">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="J16" s="14">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="K16" s="15">
-        <v>-6.25</v>
+        <v>-7.843137254901</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.419354838709</v>
+        <v>-27.131782945736</v>
       </c>
       <c r="M16" s="15">
-        <v>-17.431192660550</v>
+        <v>-19.658119658119</v>
       </c>
       <c r="N16" s="15">
-        <v>-79.020979020979</v>
+        <v>-79.249448123620</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>-41.666666666666</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F17" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G17" s="14">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H17" s="15">
-        <v>-44.444444444444</v>
+        <v>-41.818181818181</v>
       </c>
       <c r="I17" s="14">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="J17" s="14">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="K17" s="15">
-        <v>-34.224598930481</v>
+        <v>-32.653061224489</v>
       </c>
       <c r="L17" s="15">
-        <v>-32.044198895027</v>
+        <v>-30.158730158730</v>
       </c>
       <c r="M17" s="15">
-        <v>20.588235294117</v>
+        <v>23.364485981308</v>
       </c>
       <c r="N17" s="15">
-        <v>1.652892561983</v>
+        <v>-2.222222222222</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>2</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>-6.666666666666</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I18" s="14">
         <v>45</v>
       </c>
       <c r="J18" s="14">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K18" s="15">
-        <v>-31.818181818181</v>
+        <v>-32.835820895522</v>
       </c>
       <c r="L18" s="15">
-        <v>-39.189189189189</v>
+        <v>-40.789473684210</v>
       </c>
       <c r="M18" s="15">
-        <v>-60.176991150442</v>
+        <v>-61.864406779661</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.117647058823</v>
+        <v>-94.360902255639</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>100</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F19" s="14">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G19" s="14">
         <v>50</v>
       </c>
       <c r="H19" s="15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="J19" s="14">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="K19" s="15">
-        <v>-11.814345991561</v>
+        <v>-13.545816733067</v>
       </c>
       <c r="L19" s="15">
-        <v>-31.921824104234</v>
+        <v>-32.608695652173</v>
       </c>
       <c r="M19" s="15">
-        <v>50.359712230215</v>
+        <v>45.637583892617</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.774509803921</v>
+        <v>-50.343249427917</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>-28.571428571428</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F20" s="14">
         <v>26</v>
       </c>
       <c r="G20" s="14">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H20" s="15">
-        <v>52.941176470588</v>
+        <v>13.043478260869</v>
       </c>
       <c r="I20" s="14">
+        <v>94</v>
+      </c>
+      <c r="J20" s="14">
         <v>85</v>
       </c>
-      <c r="J20" s="14">
-        <v>76</v>
-      </c>
       <c r="K20" s="15">
-        <v>11.842105263157</v>
+        <v>10.588235294117</v>
       </c>
       <c r="L20" s="15">
-        <v>-9.574468085106</v>
+        <v>-7.843137254901</v>
       </c>
       <c r="M20" s="15">
-        <v>16.438356164383</v>
+        <v>22.077922077922</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.666666666666</v>
+        <v>-88.146279949558</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D21" s="17">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E21" s="18">
-        <v>-5.263157894736</v>
+        <v>-26.190476190476</v>
       </c>
       <c r="F21" s="17">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G21" s="17">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.5</v>
+        <v>-19.767441860465</v>
       </c>
       <c r="I21" s="17">
-        <v>566</v>
+        <v>596</v>
       </c>
       <c r="J21" s="17">
-        <v>678</v>
+        <v>720</v>
       </c>
       <c r="K21" s="18">
-        <v>-16.519174041297</v>
+        <v>-17.222222222222</v>
       </c>
       <c r="L21" s="18">
-        <v>-28.354430379746</v>
+        <v>-28.192771084337</v>
       </c>
       <c r="M21" s="18">
-        <v>4.235727440147</v>
+        <v>3.652173913043</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.269076305220</v>
+        <v>-77.372817008352</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>2</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
       <c r="E22" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
         <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-40</v>
+        <v>-60</v>
       </c>
       <c r="I22" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K22" s="15">
-        <v>-47.619047619047</v>
+        <v>-56.521739130434</v>
       </c>
       <c r="L22" s="15">
-        <v>-50</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>-8.333333333333</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E24" s="15">
-        <v>21.052631578947</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="F24" s="14">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G24" s="14">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.434782608695</v>
+        <v>-9.900990099009</v>
       </c>
       <c r="I24" s="14">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="J24" s="14">
-        <v>441</v>
+        <v>475</v>
       </c>
       <c r="K24" s="15">
-        <v>-8.163265306122</v>
+        <v>-10.105263157894</v>
       </c>
       <c r="L24" s="15">
-        <v>-50.549450549450</v>
+        <v>-50.058479532163</v>
       </c>
       <c r="M24" s="15">
-        <v>17.732558139534</v>
+        <v>16.986301369863</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E25" s="15">
-        <v>100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
         <v>26</v>
       </c>
       <c r="G25" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H25" s="15">
-        <v>-23.529411764705</v>
+        <v>-25.714285714285</v>
       </c>
       <c r="I25" s="14">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="J25" s="14">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="K25" s="15">
-        <v>-42.631578947368</v>
+        <v>-44.059405940594</v>
       </c>
       <c r="L25" s="15">
-        <v>-76.857749469214</v>
+        <v>-76.796714579055</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D26" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E26" s="15">
-        <v>-62.5</v>
+        <v>9.090909090909</v>
       </c>
       <c r="F26" s="14">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G26" s="14">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H26" s="15">
-        <v>-34.939759036144</v>
+        <v>-41.573033707865</v>
       </c>
       <c r="I26" s="14">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="J26" s="14">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="K26" s="15">
-        <v>-22.689075630252</v>
+        <v>-20.844327176781</v>
       </c>
       <c r="L26" s="15">
-        <v>-31.343283582089</v>
+        <v>-30.555555555555</v>
       </c>
       <c r="M26" s="15">
-        <v>-12.658227848101</v>
+        <v>-9.365558912386</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="14">
         <v>18</v>
       </c>
       <c r="J27" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L27" s="15">
-        <v>-14.285714285714</v>
+        <v>-25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E28" s="15">
-        <v>-80</v>
+        <v>50</v>
       </c>
       <c r="F28" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G28" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I28" s="14">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J28" s="14">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K28" s="15">
-        <v>5.405405405405</v>
+        <v>9.756097560975</v>
       </c>
       <c r="L28" s="15">
-        <v>-22</v>
+        <v>-13.461538461538</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,7 +1485,7 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1497,18 +1497,18 @@
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.444444444444</v>
+        <v>-89.473684210526</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,7 +1526,7 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1538,10 +1538,10 @@
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.117647058823</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="31" spans="1:14">
